--- a/artfynd/A 52503-2025 artfynd.xlsx
+++ b/artfynd/A 52503-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115046074</v>
+        <v>115046056</v>
       </c>
       <c r="B2" t="n">
-        <v>74654</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6471</v>
+        <v>145</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Klosterlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Biatoridium monasteriense</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>J.Lahm ex Körb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nogård (Nogård), Upl</t>
+          <t>Nogård, Nogård, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -765,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Stor mängd på lutande tvåstammig lönn</t>
+          <t>Östsida av lutande tvåstammig grov lön</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,15 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115046056</v>
+        <v>115046074</v>
       </c>
       <c r="B3" t="n">
-        <v>77831</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,27 +813,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>145</v>
+        <v>6471</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Klosterlav</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Biatoridium monasteriense</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>J.Lahm ex Körb.</t>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nogård (Nogård), Upl</t>
+          <t>Nogård, Nogård, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -897,7 +887,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östsida av lutande tvåstammig grov lön</t>
+          <t>Stor mängd på lutande tvåstammig lönn</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,6 +926,592 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>69517927</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91214</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>751</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kastanjesopp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Gyroporus castaneus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Bull. : Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mellantorp 7,5 km SV om Almunge kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>665183</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6636633</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 ex. intill ek och björk.  Hatt 9 cm bred, filtluden, kastanjebrun. Rör vitgula, 2-4 per mm. Fot 9 cm hög och 2,5-3 cm tjock, fint filtluden av hattens färg. Kött vitt, ej blånande, fast. I foten består köttet av en hård ca. 4 mm tjock yttre kant som är svagt kastanjebrun, medan centrala delen av foten är rent vit och mer porös med små ihåliga partier (kamrad?). Smak mild. Sporer 9-12 x 4,5-6 μm.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Naturbetesmark med inslag av ek och björk.</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>59182478</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89104</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>805</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Scharlakansvaxing</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hygrocybe punicea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mellantorp 7,5 km SV om Almunge kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>665189</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6636612</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 ex.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Naturbetesmark.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>59182454</v>
+      </c>
+      <c r="B6" t="n">
+        <v>88964</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3279</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Maskfingersvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Clavaria fragilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Holmsk., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mellantorp 7,5 km SV om Almunge kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>665182</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6636631</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca. 20 ex.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Naturbetesmark.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>59182459</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90074</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3939</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Backnopping</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Entoloma atrocoeruleum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Noordel.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mellantorp 7,5 km SV om Almunge kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>665182</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6636631</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca. 20 ex.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Naturbetesmark.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>59182466</v>
+      </c>
+      <c r="B8" t="n">
+        <v>89081</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4374</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulvaxing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hygrocybe chlorophana</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mellantorp 7,5 km SV om Almunge kyrka, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>665182</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6636631</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2001-09-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Naturbetesmark.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
